--- a/Template/timeliner-planner-template.xlsx
+++ b/Template/timeliner-planner-template.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Conversion used by the tool: 1560 h/year = 1 FTE (130 h/month). This is a fixed convention in the code, not a cell you can change here.</t>
+          <t>Conversion used by the tool: 1580 h/year = 1 FTE (131.7 h/month). This is a fixed convention in the code, not a cell you can change here.</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="C49" s="12" t="n"/>
       <c r="D49" s="20">
-        <f>D48/1560</f>
+        <f>D48/1580</f>
         <v/>
       </c>
     </row>

--- a/Template/timeliner-planner-template.xlsx
+++ b/Template/timeliner-planner-template.xlsx
@@ -13,6 +13,8 @@
     <sheet name="gates-system" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="gates-hc" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="mg-hc" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="capacity" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="baseline" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,8 +23,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -182,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -266,6 +269,14 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -693,7 +704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F54"/>
+  <dimension ref="A2:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -888,85 +899,85 @@
       <c r="E16" s="12" t="n"/>
       <c r="F16" s="12" t="n"/>
     </row>
-    <row r="18">
-      <c r="B18" s="3" t="inlineStr">
+    <row r="17" ht="28" customHeight="1">
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Yes, row 1</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>OPTIONAL. A = unit, B = from, C = to, D = FTE. How many people a unit has over a period; rows for one unit add up. Drives the over-capacity warnings and the Capacity view.</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Written by the tool</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>OPTIONAL. Filled in when you press “Capture baseline”. Freezes the plan so the Drift view can show what moved since.</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Columns of the "plan" tab</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Header</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="8" t="n"/>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>Ref</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>Your own reference. Used as the track ID only when column C is empty; otherwise free text.</t>
-        </is>
-      </c>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>Shown on the bar. Square brackets are stripped out.</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Track</t>
+          <t>Ref</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>THE KEY FIELD. One chart row per distinct value. Deliverables sharing a track stack on the same line, and two that overlap in time are flagged as a collision.</t>
+          <t>Your own reference. Used as the track ID only when column C is empty; otherwise free text.</t>
         </is>
       </c>
       <c r="E22" s="12" t="n"/>
@@ -975,17 +986,17 @@
     <row r="23" ht="26" customHeight="1">
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Stage</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Which band the track belongs to. Fill it on the track's first row only - the other rows inherit it. A track belongs to exactly one stage, so do not spread one track across several stages.</t>
+          <t>Shown on the bar. Square brackets are stripped out.</t>
         </is>
       </c>
       <c r="E23" s="12" t="n"/>
@@ -994,17 +1005,17 @@
     <row r="24" ht="26" customHeight="1">
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Track</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>A number. Man-hours when column K is empty, a monetary amount when column K says EUR.</t>
+          <t>THE KEY FIELD. One chart row per distinct value. Deliverables sharing a track stack on the same line, and two that overlap in time are flagged as a collision.</t>
         </is>
       </c>
       <c r="E24" s="12" t="n"/>
@@ -1013,17 +1024,17 @@
     <row r="25" ht="26" customHeight="1">
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Stage</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>A real date. Type N/A (or leave blank) to park a deliverable: the row is then skipped.</t>
+          <t>Which band the track belongs to. Fill it on the track's first row only - the other rows inherit it. A track belongs to exactly one stage, so do not spread one track across several stages.</t>
         </is>
       </c>
       <c r="E25" s="12" t="n"/>
@@ -1032,17 +1043,17 @@
     <row r="26" ht="26" customHeight="1">
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>End</t>
+          <t>Amount</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>A real date, inclusive. If it is earlier than the start the planner swaps the two.</t>
+          <t>A number. Man-hours when column K is empty, a monetary amount when column K says EUR.</t>
         </is>
       </c>
       <c r="E26" s="12" t="n"/>
@@ -1051,17 +1062,17 @@
     <row r="27" ht="26" customHeight="1">
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>Comment</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Free text, shown in the tooltip and in brackets after the title.</t>
+          <t>A real date. Type N/A (or leave blank) to park a deliverable: the row is then skipped.</t>
         </is>
       </c>
       <c r="E27" s="12" t="n"/>
@@ -1070,17 +1081,17 @@
     <row r="28" ht="26" customHeight="1">
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="inlineStr">
-        <is>
-          <t>Owner</t>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>End</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Free column, IGNORED by the planner. Yours to use.</t>
+          <t>A real date, inclusive. If it is earlier than the start the planner swaps the two.</t>
         </is>
       </c>
       <c r="E28" s="12" t="n"/>
@@ -1089,17 +1100,17 @@
     <row r="29" ht="26" customHeight="1">
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C29" s="15" t="inlineStr">
-        <is>
-          <t>Status</t>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>Comment</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Free column, IGNORED by the planner. Yours to use.</t>
+          <t>Free text, shown in the tooltip and in brackets after the title.</t>
         </is>
       </c>
       <c r="E29" s="12" t="n"/>
@@ -1108,17 +1119,17 @@
     <row r="30" ht="26" customHeight="1">
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="inlineStr">
-        <is>
-          <t>Currency</t>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Owner</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>EUR (or euro / the euro sign) marks a monetary item, drawn in green and totalled separately. Anything else, including blank, means man-hours.</t>
+          <t>Free column, IGNORED by the planner. Yours to use.</t>
         </is>
       </c>
       <c r="E30" s="12" t="n"/>
@@ -1127,50 +1138,64 @@
     <row r="31" ht="26" customHeight="1">
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>Unit</t>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Department or team. Drives the filter chips and the per-unit colour. Blank becomes "Unassigned".</t>
+          <t>Free column, IGNORED by the planner. Yours to use.</t>
         </is>
       </c>
       <c r="E31" s="12" t="n"/>
       <c r="F31" s="12" t="n"/>
     </row>
-    <row r="33">
-      <c r="B33" s="3" t="inlineStr">
+    <row r="32" ht="26" customHeight="1">
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>EUR (or euro / the euro sign) marks a monetary item, drawn in green and totalled separately. Anything else, including blank, means man-hours.</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Department or team. Drives the filter chips and the per-unit colour. Blank becomes "Unassigned".</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="12" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Rules worth knowing</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Dates: type them as real dates. The planner also reads dd/mm/yyyy and yyyy-mm-dd text, but real dates avoid any ambiguity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>A row is only plotted when BOTH dates are readable. Everything else is skipped and reported in the status bar.</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1207,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Effort is spread evenly over the days of a deliverable, which is how the monthly FTE curve and the yearly summary are built.</t>
+          <t>Dates: type them as real dates. The planner also reads dd/mm/yyyy and yyyy-mm-dd text, but real dates avoid any ambiguity.</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1219,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Conversion used by the tool: 1580 h/year = 1 FTE (131.7 h/month). This is a fixed convention in the code, not a cell you can change here.</t>
+          <t>A row is only plotted when BOTH dates are readable. Everything else is skipped and reported in the status bar.</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1231,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Columns can be moved if you rename the header: the planner recognises, among others, Title/Titre, Track/ID, Stage/Phase, Amount/Montant, Start/Debut, End/Fin, Currency/Devise, Unit/Departement. Leave the layout as-is and you never have to think about it.</t>
+          <t>Effort is spread evenly over the days of a deliverable, which is how the monthly FTE curve and the yearly summary are built.</t>
         </is>
       </c>
     </row>
@@ -1218,178 +1243,230 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Adding extra tabs is safe - only the five named tabs are read.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="3" t="inlineStr">
+          <t>Conversion used by the tool: 1580 h/year = 1 FTE (131.7 h/month). This is a fixed convention in the code, not a cell you can change here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Columns can be moved if you rename the header: the planner recognises, among others, Title/Titre, Track/ID, Stage/Phase, Amount/Montant, Start/Debut, End/Fin, Currency/Devise, Unit/Departement. Leave the layout as-is and you never have to think about it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Adding extra tabs is safe - only the named tabs are read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>The planner can edit the plan tab back: drag a bar sideways to reschedule it, drag it onto another track to move it there, double-click an empty spot on a track to create a deliverable, and use the editor to change the title, track, stage, dates, amount, currency, unit and comment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Removing a deliverable from the chart only blanks its two date cells (they become N/A). The row, its title and its amount stay in the sheet, and setting dates again brings it straight back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Cross-check (recomputed from the plan tab)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="16" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>These cells mirror what the planner should display. If a figure looks wrong, the data is wrong.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="17" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="17" t="inlineStr">
         <is>
           <t>Deliverables listed</t>
         </is>
       </c>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="18">
+      <c r="C48" s="12" t="n"/>
+      <c r="D48" s="18">
         <f>COUNTA(plan!$B$2:$B$120)</f>
         <v/>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="17" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>Deliverables plotted</t>
         </is>
       </c>
-      <c r="C45" s="12" t="n"/>
-      <c r="D45" s="18">
+      <c r="C49" s="12" t="n"/>
+      <c r="D49" s="18">
         <f>COUNTIFS(plan!$F$2:$F$120,"&gt;=1",plan!$G$2:$G$120,"&gt;=1")</f>
         <v/>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="17" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="17" t="inlineStr">
         <is>
           <t>Rows skipped (no dates)</t>
         </is>
       </c>
-      <c r="C46" s="12" t="n"/>
-      <c r="D46" s="18">
-        <f>D44-D45</f>
+      <c r="C50" s="12" t="n"/>
+      <c r="D50" s="18">
+        <f>D48-D49</f>
         <v/>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="17" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="17" t="inlineStr">
         <is>
           <t>Distinct tracks plotted</t>
         </is>
       </c>
-      <c r="C47" s="12" t="n"/>
-      <c r="D47" s="18">
+      <c r="C51" s="12" t="n"/>
+      <c r="D51" s="18">
         <f>SUMPRODUCT((plan!$C$2:$C$120&lt;&gt;"")*ISNUMBER(plan!$F$2:$F$120)*ISNUMBER(plan!$G$2:$G$120)/(COUNTIFS(plan!$C$2:$C$120,plan!$C$2:$C$120&amp;"",plan!$F$2:$F$120,"&gt;=1",plan!$G$2:$G$120,"&gt;=1")+1-(plan!$C$2:$C$120&lt;&gt;"")*ISNUMBER(plan!$F$2:$F$120)*ISNUMBER(plan!$G$2:$G$120)))</f>
         <v/>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="17" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="17" t="inlineStr">
         <is>
           <t>Total effort (Mh)</t>
         </is>
       </c>
-      <c r="C48" s="12" t="n"/>
-      <c r="D48" s="19">
+      <c r="C52" s="12" t="n"/>
+      <c r="D52" s="19">
         <f>SUMIFS(plan!$E$2:$E$120,plan!$K$2:$K$120,"&lt;&gt;EUR",plan!$F$2:$F$120,"&gt;=1",plan!$G$2:$G$120,"&gt;=1")</f>
         <v/>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="17" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="17" t="inlineStr">
         <is>
           <t>Equivalent FTE-years</t>
         </is>
       </c>
-      <c r="C49" s="12" t="n"/>
-      <c r="D49" s="20">
-        <f>D48/1580</f>
+      <c r="C53" s="12" t="n"/>
+      <c r="D53" s="20">
+        <f>D52/1580</f>
         <v/>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="17" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="17" t="inlineStr">
         <is>
           <t>Total budget (EUR)</t>
         </is>
       </c>
-      <c r="C50" s="12" t="n"/>
-      <c r="D50" s="19">
+      <c r="C54" s="12" t="n"/>
+      <c r="D54" s="19">
         <f>SUMIFS(plan!$E$2:$E$120,plan!$K$2:$K$120,"EUR",plan!$F$2:$F$120,"&gt;=1",plan!$G$2:$G$120,"&gt;=1")</f>
         <v/>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="17" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="17" t="inlineStr">
         <is>
           <t>Earliest start</t>
         </is>
       </c>
-      <c r="C51" s="12" t="n"/>
-      <c r="D51" s="21">
+      <c r="C55" s="12" t="n"/>
+      <c r="D55" s="21">
         <f>MIN(plan!$F$2:$F$120)</f>
         <v/>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="17" t="inlineStr">
+    <row r="56">
+      <c r="B56" s="17" t="inlineStr">
         <is>
           <t>Latest end</t>
         </is>
       </c>
-      <c r="C52" s="12" t="n"/>
-      <c r="D52" s="21">
+      <c r="C56" s="12" t="n"/>
+      <c r="D56" s="21">
         <f>MAX(plan!$G$2:$G$120)</f>
         <v/>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="22" t="inlineStr">
+    <row r="58">
+      <c r="B58" s="22" t="inlineStr">
         <is>
           <t>Sample data is illustrative only - a fictitious product-development programme. Replace it entirely.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="B47:C47"/>
+  <mergeCells count="44">
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="D27:F27"/>
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="C8:F8"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D32:F32"/>
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="C38:F38"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B56:C56"/>
     <mergeCell ref="C37:F37"/>
     <mergeCell ref="D16:F16"/>
+    <mergeCell ref="B58:F58"/>
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="B48:C48"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="B42:F42"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D18:F18"/>
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="D25:F25"/>
+    <mergeCell ref="C42:F42"/>
     <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="B53:C53"/>
     <mergeCell ref="D24:F24"/>
-    <mergeCell ref="B44:C44"/>
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="D29:F29"/>
     <mergeCell ref="D23:F23"/>
-    <mergeCell ref="C35:F35"/>
     <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="C41:F41"/>
     <mergeCell ref="B49:C49"/>
+    <mergeCell ref="C40:F40"/>
     <mergeCell ref="C9:F9"/>
-    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="B55:C55"/>
     <mergeCell ref="D31:F31"/>
+    <mergeCell ref="C43:F43"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="D22:F22"/>
-    <mergeCell ref="B45:C45"/>
     <mergeCell ref="B50:C50"/>
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="C36:F36"/>
@@ -4568,4 +4645,333 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>FTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>Program</t>
+        </is>
+      </c>
+      <c r="B2" s="35" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C2" s="35" t="n">
+        <v>46752</v>
+      </c>
+      <c r="D2" s="36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>OPTIONAL TAB. How many people each unit actually has, as periods rather than a month grid: a ramp-up is one row, not twelve. Rows for the same unit ADD UP - see Mechanical, which gets half an extra FTE from mid-2026, a contractor. The planner compares this with the effort your plan demands and flags the months where a unit is short. Delete the tab and the feature simply switches off. Only man-hour deliverables create demand: a line in EUR buys an outcome, it does not occupy anyone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t>Systems</t>
+        </is>
+      </c>
+      <c r="B3" s="35" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C3" s="35" t="n">
+        <v>46752</v>
+      </c>
+      <c r="D3" s="36" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>Mechanical</t>
+        </is>
+      </c>
+      <c r="B4" s="35" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C4" s="35" t="n">
+        <v>46752</v>
+      </c>
+      <c r="D4" s="36" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C5" s="35" t="n">
+        <v>46752</v>
+      </c>
+      <c r="D5" s="36" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C6" s="35" t="n">
+        <v>46752</v>
+      </c>
+      <c r="D6" s="36" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C7" s="35" t="n">
+        <v>46752</v>
+      </c>
+      <c r="D7" s="36" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C8" s="35" t="n">
+        <v>46752</v>
+      </c>
+      <c r="D8" s="36" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>Purchasing</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C9" s="35" t="n">
+        <v>46752</v>
+      </c>
+      <c r="D9" s="36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="37" t="n"/>
+      <c r="B10" s="38" t="n"/>
+      <c r="C10" s="38" t="n"/>
+      <c r="D10" s="37" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="37" t="n"/>
+      <c r="B11" s="38" t="n"/>
+      <c r="C11" s="38" t="n"/>
+      <c r="D11" s="37" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="37" t="n"/>
+      <c r="B12" s="38" t="n"/>
+      <c r="C12" s="38" t="n"/>
+      <c r="D12" s="37" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="37" t="n"/>
+      <c r="B13" s="38" t="n"/>
+      <c r="C13" s="38" t="n"/>
+      <c r="D13" s="37" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="37" t="n"/>
+      <c r="B14" s="38" t="n"/>
+      <c r="C14" s="38" t="n"/>
+      <c r="D14" s="37" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="37" t="n"/>
+      <c r="B15" s="38" t="n"/>
+      <c r="C15" s="38" t="n"/>
+      <c r="D15" s="37" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="37" t="n"/>
+      <c r="B16" s="38" t="n"/>
+      <c r="C16" s="38" t="n"/>
+      <c r="D16" s="37" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="37" t="n"/>
+      <c r="B17" s="38" t="n"/>
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="37" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="37" t="n"/>
+      <c r="B18" s="38" t="n"/>
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="37" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="37" t="n"/>
+      <c r="B19" s="38" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="37" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="37" t="n"/>
+      <c r="B20" s="38" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="37" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="37" t="n"/>
+      <c r="B21" s="38" t="n"/>
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="37" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F2:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Plan row</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Track</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>End</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Captured at</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="I2" s="16" t="inlineStr">
+        <is>
+          <t>OPTIONAL TAB, WRITTEN BY THE TOOL - do not fill it in by hand. Press “Capture baseline” in the planner's Drift view and today's dates and amounts are frozen here. From then on every bar shows a hollow ghost where it used to sit, and the Drift view lists what slipped, by how many days, and how much effort was added or removed. Re-capturing overwrites it; clearing empties it. Leave the tab out entirely and the planner just creates it when you first capture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I2:I9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>